--- a/Data/Export/Common/Buff_状态.xlsx
+++ b/Data/Export/Common/Buff_状态.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr updateLinks="always" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="J:\sango_infinity\Data\Export\Common\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\sango_infinity\Data\Export\Common\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48C5C302-CFE6-4250-AE3A-A9A162A8A103}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{939F8584-5152-4196-A5AD-829095806249}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" tabRatio="923" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="923" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Buffs" sheetId="36" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="34">
   <si>
     <t>序号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -140,6 +140,30 @@
   </si>
   <si>
     <t>Assets/Effect/Prefab/ef_buff_escape.prefab</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>增加防御</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>增加攻击</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>limit</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>限制</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"AddAttack", value:10}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"AddDefence", value:10}]</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -622,21 +646,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B0F1D98-4B0B-4096-90A4-E28636B1D41A}">
   <dimension ref="A1:X69"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15" style="2" customWidth="1"/>
-    <col min="2" max="3" width="9" style="2"/>
-    <col min="4" max="4" width="9.6640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="9.6640625" style="2" customWidth="1"/>
-    <col min="7" max="7" width="48.21875" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.77734375" style="2" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="95.33203125" style="2" customWidth="1"/>
-    <col min="10" max="10" width="10.44140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="19.44140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9" style="2"/>
+    <col min="3" max="3" width="11.54296875" style="2" customWidth="1"/>
+    <col min="4" max="4" width="9.6328125" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="9.6328125" style="2" customWidth="1"/>
+    <col min="7" max="7" width="48.1796875" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.1796875" style="2" customWidth="1"/>
+    <col min="9" max="9" width="95.36328125" style="2" customWidth="1"/>
+    <col min="10" max="10" width="10.453125" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="19.453125" style="2" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="17" style="2" customWidth="1"/>
-    <col min="13" max="14" width="10.77734375" style="2" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="6.21875" style="2" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="8.44140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="10.81640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="6.1796875" style="2" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="8.453125" style="2" bestFit="1" customWidth="1"/>
     <col min="17" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
@@ -654,7 +679,9 @@
       <c r="E1" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="F1" s="14"/>
+      <c r="F1" s="14" t="s">
+        <v>31</v>
+      </c>
       <c r="G1" s="14" t="s">
         <v>13</v>
       </c>
@@ -724,7 +751,9 @@
       <c r="E3" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="8"/>
+      <c r="F3" s="8" t="s">
+        <v>30</v>
+      </c>
       <c r="G3" s="8" t="s">
         <v>14</v>
       </c>
@@ -767,7 +796,7 @@
         <v>18</v>
       </c>
       <c r="F4" s="15" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="G4" s="15" t="s">
         <v>3</v>
@@ -796,7 +825,9 @@
       <c r="E5" s="4">
         <v>1</v>
       </c>
-      <c r="F5" s="4"/>
+      <c r="F5" s="4">
+        <v>0</v>
+      </c>
       <c r="G5" s="4" t="s">
         <v>15</v>
       </c>
@@ -831,7 +862,9 @@
       <c r="E6" s="4">
         <v>2</v>
       </c>
-      <c r="F6" s="4"/>
+      <c r="F6" s="4">
+        <v>0</v>
+      </c>
       <c r="G6" s="4" t="s">
         <v>27</v>
       </c>
@@ -853,13 +886,26 @@
       <c r="W6" s="4"/>
     </row>
     <row r="7" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="B7" s="4"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="4"/>
-      <c r="E7" s="4"/>
-      <c r="F7" s="4"/>
+      <c r="B7" s="4">
+        <v>3</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D7" s="4">
+        <v>2</v>
+      </c>
+      <c r="E7" s="4">
+        <v>3</v>
+      </c>
+      <c r="F7" s="4">
+        <v>1</v>
+      </c>
       <c r="G7" s="4"/>
       <c r="H7" s="4"/>
+      <c r="I7" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="L7" s="6"/>
       <c r="M7" s="4"/>
       <c r="N7" s="4"/>
@@ -872,13 +918,26 @@
       <c r="W7" s="4"/>
     </row>
     <row r="8" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="B8" s="4"/>
-      <c r="C8" s="4"/>
-      <c r="D8" s="4"/>
-      <c r="E8" s="4"/>
-      <c r="F8" s="4"/>
+      <c r="B8" s="4">
+        <v>4</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D8" s="4">
+        <v>2</v>
+      </c>
+      <c r="E8" s="4">
+        <v>4</v>
+      </c>
+      <c r="F8" s="4">
+        <v>1</v>
+      </c>
       <c r="G8" s="4"/>
       <c r="H8" s="4"/>
+      <c r="I8" s="2" t="s">
+        <v>32</v>
+      </c>
       <c r="L8" s="6"/>
       <c r="M8" s="4"/>
       <c r="N8" s="4"/>
